--- a/public/asset/template_siswa.xlsx
+++ b/public/asset/template_siswa.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\SIMPEL-5\public\import_guru_siswa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\SIMPEL-5\public\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABFF998-3775-4D43-BC68-AA1DC3359650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DECFBE7-12AE-480C-AEA5-8B77AE1F9410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B5C1236F-2DC1-4DEB-9CB8-AC0626038A09}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="230">
   <si>
     <t>nama</t>
   </si>
@@ -54,29 +54,683 @@
     <t>email</t>
   </si>
   <si>
-    <t>siswa5@gmail.com</t>
-  </si>
-  <si>
-    <t>siswa6@gmail.com</t>
-  </si>
-  <si>
-    <t>Multimedia</t>
-  </si>
-  <si>
-    <t>11 MM 1</t>
-  </si>
-  <si>
-    <t>Siswa 5 import</t>
-  </si>
-  <si>
-    <t>Siswa 6 import</t>
+    <t>Desain Komunikasi Visual</t>
+  </si>
+  <si>
+    <t>11 DKV 1</t>
+  </si>
+  <si>
+    <t>Abdurropi</t>
+  </si>
+  <si>
+    <t>Agustinus Adi Kristanto</t>
+  </si>
+  <si>
+    <t>Akbar Maulana Pane</t>
+  </si>
+  <si>
+    <t>Ananda Sukma Rosdani</t>
+  </si>
+  <si>
+    <t>Andrio Dhirgham Fatih</t>
+  </si>
+  <si>
+    <t>Ardhana Ekhsa Ramanda</t>
+  </si>
+  <si>
+    <t>Azfar Maula</t>
+  </si>
+  <si>
+    <t>Bagas Aribawa</t>
+  </si>
+  <si>
+    <t>Cikal Yusi Amelia</t>
+  </si>
+  <si>
+    <t>Cristina Yuni Arta</t>
+  </si>
+  <si>
+    <t>Dimas Andrian Yudistira</t>
+  </si>
+  <si>
+    <t>Fadlan Saefulloh</t>
+  </si>
+  <si>
+    <t>Gadiza Rahma Khairunnisaa</t>
+  </si>
+  <si>
+    <t>Hadiyana Kusuma</t>
+  </si>
+  <si>
+    <t>Haerunisa Dwirianti</t>
+  </si>
+  <si>
+    <t>Indra Jonathan Sinaga</t>
+  </si>
+  <si>
+    <t>Iqbal Andrean Maulana</t>
+  </si>
+  <si>
+    <t>Jhon Erick Hamonangan Sinaga</t>
+  </si>
+  <si>
+    <t>Josua Fernando Hutabarat</t>
+  </si>
+  <si>
+    <t>Maysi</t>
+  </si>
+  <si>
+    <t>Melvin Novallino</t>
+  </si>
+  <si>
+    <t>Muhamad Syahril Luthfi Hakim</t>
+  </si>
+  <si>
+    <t>Muhammad Guntur</t>
+  </si>
+  <si>
+    <t>Muhammad Nurhidayat</t>
+  </si>
+  <si>
+    <t>Muhammad Renaldi Firdaus</t>
+  </si>
+  <si>
+    <t>Muhammad Sultoni</t>
+  </si>
+  <si>
+    <t>Nala Mufthi</t>
+  </si>
+  <si>
+    <t>Putri Andini</t>
+  </si>
+  <si>
+    <t>Rafif Kholisaputra</t>
+  </si>
+  <si>
+    <t>Rahman Triyono</t>
+  </si>
+  <si>
+    <t>Raka Harun Alrasyid</t>
+  </si>
+  <si>
+    <t>Ririn Dwi Nuryanti</t>
+  </si>
+  <si>
+    <t>Safira Salsabilah</t>
+  </si>
+  <si>
+    <t>Salsabila Az Zahra</t>
+  </si>
+  <si>
+    <t>Shalu Mauliddia Fanesha</t>
+  </si>
+  <si>
+    <t>Siti Zalfa Mauliyah</t>
+  </si>
+  <si>
+    <t>Tegar Restu Tama Alistia</t>
+  </si>
+  <si>
+    <t>U'Baidillaah</t>
+  </si>
+  <si>
+    <t>Aldianur Isllam</t>
+  </si>
+  <si>
+    <t>Andhy Febriyansyah</t>
+  </si>
+  <si>
+    <t>Aninda Puspitha</t>
+  </si>
+  <si>
+    <t>Arief Rachman Hidayat</t>
+  </si>
+  <si>
+    <t>Arifin Dian Nugraha</t>
+  </si>
+  <si>
+    <t>Bachtiyar Siregar</t>
+  </si>
+  <si>
+    <t>Baruna Wira Saputra</t>
+  </si>
+  <si>
+    <t>Cindy Agustina</t>
+  </si>
+  <si>
+    <t>Daffa Alwansyah Haryadi</t>
+  </si>
+  <si>
+    <t>Dimas Nurwahid</t>
+  </si>
+  <si>
+    <t>Eksa Mulyana Nur Rizki</t>
+  </si>
+  <si>
+    <t>Erwin Ismail</t>
+  </si>
+  <si>
+    <t>Fabian Aditiya Putra Zayansyah</t>
+  </si>
+  <si>
+    <t>Fadillah Maulana</t>
+  </si>
+  <si>
+    <t>Fajar Nur Hidayat</t>
+  </si>
+  <si>
+    <t>Farel Adi Wibowo</t>
+  </si>
+  <si>
+    <t>Ferdian Rendi Ahksani</t>
+  </si>
+  <si>
+    <t>Gilang Adhitya Ramadhan</t>
+  </si>
+  <si>
+    <t>Imelda Wijaya</t>
+  </si>
+  <si>
+    <t>Indah Setia Ningsih</t>
+  </si>
+  <si>
+    <t>Jihan Nadhifah Harditya</t>
+  </si>
+  <si>
+    <t>Kartika Melodia</t>
+  </si>
+  <si>
+    <t>Marsheila Ananda Firly</t>
+  </si>
+  <si>
+    <t>Mochamad Tegar Yusmar</t>
+  </si>
+  <si>
+    <t>Muhammad Hafid Rahman</t>
+  </si>
+  <si>
+    <t>Muhammad Thoriq</t>
+  </si>
+  <si>
+    <t>Nino Anggoro Pratama</t>
+  </si>
+  <si>
+    <t>Puspa Desyha Anyelir</t>
+  </si>
+  <si>
+    <t>Ravita Ramadhani Putri</t>
+  </si>
+  <si>
+    <t>Rizki Aditia</t>
+  </si>
+  <si>
+    <t>Salma Mutia</t>
+  </si>
+  <si>
+    <t>Sherly Aulia Khairunnisa</t>
+  </si>
+  <si>
+    <t>Tika Ameylia</t>
+  </si>
+  <si>
+    <t>Widia Nirmala Putri</t>
+  </si>
+  <si>
+    <t>Yudha Pradipta Purwanto</t>
+  </si>
+  <si>
+    <t>Zulfikar</t>
+  </si>
+  <si>
+    <t>Ahmad Hamdani</t>
+  </si>
+  <si>
+    <t>Ahmad Kadafi</t>
+  </si>
+  <si>
+    <t>Al Fauzi Pebrian</t>
+  </si>
+  <si>
+    <t>Andre Eka Rahmadani</t>
+  </si>
+  <si>
+    <t>Andrian Ramadani</t>
+  </si>
+  <si>
+    <t>Angga Putra Bintang Agustiansyah</t>
+  </si>
+  <si>
+    <t>Anisah Agustina</t>
+  </si>
+  <si>
+    <t>Anyelir Putri Septiandini</t>
+  </si>
+  <si>
+    <t>Dzaky Ra'If Hafizh</t>
+  </si>
+  <si>
+    <t>Erlang Syahputra Ginting</t>
+  </si>
+  <si>
+    <t>Farhan Kamil</t>
+  </si>
+  <si>
+    <t>Fatsyah Wijaya Mulya</t>
+  </si>
+  <si>
+    <t>Ferri Efendi</t>
+  </si>
+  <si>
+    <t>Frischa Claudya Silitonga</t>
+  </si>
+  <si>
+    <t>Husnul Khotimah</t>
+  </si>
+  <si>
+    <t>Khasifatu Ramadhani</t>
+  </si>
+  <si>
+    <t>Khusnul Khatimah</t>
+  </si>
+  <si>
+    <t>Lintang Sabila Naura</t>
+  </si>
+  <si>
+    <t>Malik Ahmad</t>
+  </si>
+  <si>
+    <t>Marco Hubertus Suwito</t>
+  </si>
+  <si>
+    <t>Masayu</t>
+  </si>
+  <si>
+    <t>Muhamad Rizki Kurniawan</t>
+  </si>
+  <si>
+    <t>Muhamad Rizky Saputra</t>
+  </si>
+  <si>
+    <t>Muhammad Isya Zidan Maulana</t>
+  </si>
+  <si>
+    <t>Muhammad Rifqi Azizan</t>
+  </si>
+  <si>
+    <t>Neneng Syekh Tiara</t>
+  </si>
+  <si>
+    <t>Rayhan Ashabul Kahfi</t>
+  </si>
+  <si>
+    <t>Reno Yudy Setiawan</t>
+  </si>
+  <si>
+    <t>Ridho Abdul Hafidz</t>
+  </si>
+  <si>
+    <t>Rido Fajar Pratama</t>
+  </si>
+  <si>
+    <t>Rizal Ardiansah Putra</t>
+  </si>
+  <si>
+    <t>Shofiyana Salsabil Fadhilah</t>
+  </si>
+  <si>
+    <t>Valencia Eliyandho</t>
+  </si>
+  <si>
+    <t>Verry Andriansyah</t>
+  </si>
+  <si>
+    <t>Vina Fitriyani</t>
+  </si>
+  <si>
+    <t>Zairani</t>
+  </si>
+  <si>
+    <t>11 DKV 2</t>
+  </si>
+  <si>
+    <t>11 DKV 3</t>
+  </si>
+  <si>
+    <t>muhammad699@gmail.com</t>
+  </si>
+  <si>
+    <t>baruna272@gmail.com</t>
+  </si>
+  <si>
+    <t>muhammad637@gmail.com</t>
+  </si>
+  <si>
+    <t>abdurropi575@gmail.com</t>
+  </si>
+  <si>
+    <t>agustinus695@gmail.com</t>
+  </si>
+  <si>
+    <t>akbar967@gmail.com</t>
+  </si>
+  <si>
+    <t>ananda252@gmail.com</t>
+  </si>
+  <si>
+    <t>andrio501@gmail.com</t>
+  </si>
+  <si>
+    <t>ardhana444@gmail.com</t>
+  </si>
+  <si>
+    <t>azfar517@gmail.com</t>
+  </si>
+  <si>
+    <t>bagas566@gmail.com</t>
+  </si>
+  <si>
+    <t>cikal224@gmail.com</t>
+  </si>
+  <si>
+    <t>cristina525@gmail.com</t>
+  </si>
+  <si>
+    <t>dimas873@gmail.com</t>
+  </si>
+  <si>
+    <t>fadlan915@gmail.com</t>
+  </si>
+  <si>
+    <t>gadiza267@gmail.com</t>
+  </si>
+  <si>
+    <t>hadiyana983@gmail.com</t>
+  </si>
+  <si>
+    <t>haerunisa467@gmail.com</t>
+  </si>
+  <si>
+    <t>indra198@gmail.com</t>
+  </si>
+  <si>
+    <t>iqbal536@gmail.com</t>
+  </si>
+  <si>
+    <t>jhon127@gmail.com</t>
+  </si>
+  <si>
+    <t>josua943@gmail.com</t>
+  </si>
+  <si>
+    <t>maysi641@gmail.com</t>
+  </si>
+  <si>
+    <t>melvin906@gmail.com</t>
+  </si>
+  <si>
+    <t>muhamad660@gmail.com</t>
+  </si>
+  <si>
+    <t>muhammad349@gmail.com</t>
+  </si>
+  <si>
+    <t>muhammad641@gmail.com</t>
+  </si>
+  <si>
+    <t>nala569@gmail.com</t>
+  </si>
+  <si>
+    <t>putri471@gmail.com</t>
+  </si>
+  <si>
+    <t>rafif951@gmail.com</t>
+  </si>
+  <si>
+    <t>rahman820@gmail.com</t>
+  </si>
+  <si>
+    <t>raka412@gmail.com</t>
+  </si>
+  <si>
+    <t>ririn338@gmail.com</t>
+  </si>
+  <si>
+    <t>safira783@gmail.com</t>
+  </si>
+  <si>
+    <t>salsabila914@gmail.com</t>
+  </si>
+  <si>
+    <t>shalu352@gmail.com</t>
+  </si>
+  <si>
+    <t>siti175@gmail.com</t>
+  </si>
+  <si>
+    <t>tegar353@gmail.com</t>
+  </si>
+  <si>
+    <t>u'baidillaah469@gmail.com</t>
+  </si>
+  <si>
+    <t>aldianur866@gmail.com</t>
+  </si>
+  <si>
+    <t>andhy826@gmail.com</t>
+  </si>
+  <si>
+    <t>aninda290@gmail.com</t>
+  </si>
+  <si>
+    <t>arief133@gmail.com</t>
+  </si>
+  <si>
+    <t>arifin557@gmail.com</t>
+  </si>
+  <si>
+    <t>bachtiyar968@gmail.com</t>
+  </si>
+  <si>
+    <t>cindy576@gmail.com</t>
+  </si>
+  <si>
+    <t>daffa948@gmail.com</t>
+  </si>
+  <si>
+    <t>dimas174@gmail.com</t>
+  </si>
+  <si>
+    <t>eksa115@gmail.com</t>
+  </si>
+  <si>
+    <t>erwin456@gmail.com</t>
+  </si>
+  <si>
+    <t>fabian651@gmail.com</t>
+  </si>
+  <si>
+    <t>fadillah314@gmail.com</t>
+  </si>
+  <si>
+    <t>fajar706@gmail.com</t>
+  </si>
+  <si>
+    <t>farel110@gmail.com</t>
+  </si>
+  <si>
+    <t>ferdian119@gmail.com</t>
+  </si>
+  <si>
+    <t>gilang664@gmail.com</t>
+  </si>
+  <si>
+    <t>imelda985@gmail.com</t>
+  </si>
+  <si>
+    <t>indah200@gmail.com</t>
+  </si>
+  <si>
+    <t>jihan717@gmail.com</t>
+  </si>
+  <si>
+    <t>kartika938@gmail.com</t>
+  </si>
+  <si>
+    <t>marsheila727@gmail.com</t>
+  </si>
+  <si>
+    <t>mochamad310@gmail.com</t>
+  </si>
+  <si>
+    <t>muhammad266@gmail.com</t>
+  </si>
+  <si>
+    <t>muhammad314@gmail.com</t>
+  </si>
+  <si>
+    <t>nino879@gmail.com</t>
+  </si>
+  <si>
+    <t>puspa463@gmail.com</t>
+  </si>
+  <si>
+    <t>ravita113@gmail.com</t>
+  </si>
+  <si>
+    <t>rizki764@gmail.com</t>
+  </si>
+  <si>
+    <t>salma737@gmail.com</t>
+  </si>
+  <si>
+    <t>sherly848@gmail.com</t>
+  </si>
+  <si>
+    <t>tika582@gmail.com</t>
+  </si>
+  <si>
+    <t>widia574@gmail.com</t>
+  </si>
+  <si>
+    <t>yudha886@gmail.com</t>
+  </si>
+  <si>
+    <t>zulfikar888@gmail.com</t>
+  </si>
+  <si>
+    <t>ahmad903@gmail.com</t>
+  </si>
+  <si>
+    <t>ahmad759@gmail.com</t>
+  </si>
+  <si>
+    <t>al323@gmail.com</t>
+  </si>
+  <si>
+    <t>andre171@gmail.com</t>
+  </si>
+  <si>
+    <t>andrian973@gmail.com</t>
+  </si>
+  <si>
+    <t>angga734@gmail.com</t>
+  </si>
+  <si>
+    <t>anisah457@gmail.com</t>
+  </si>
+  <si>
+    <t>anyelir852@gmail.com</t>
+  </si>
+  <si>
+    <t>dzaky555@gmail.com</t>
+  </si>
+  <si>
+    <t>erlang746@gmail.com</t>
+  </si>
+  <si>
+    <t>farhan281@gmail.com</t>
+  </si>
+  <si>
+    <t>fatsyah809@gmail.com</t>
+  </si>
+  <si>
+    <t>ferri567@gmail.com</t>
+  </si>
+  <si>
+    <t>frischa548@gmail.com</t>
+  </si>
+  <si>
+    <t>husnul628@gmail.com</t>
+  </si>
+  <si>
+    <t>khasifatu672@gmail.com</t>
+  </si>
+  <si>
+    <t>khusnul604@gmail.com</t>
+  </si>
+  <si>
+    <t>lintang651@gmail.com</t>
+  </si>
+  <si>
+    <t>malik149@gmail.com</t>
+  </si>
+  <si>
+    <t>marco188@gmail.com</t>
+  </si>
+  <si>
+    <t>masayu898@gmail.com</t>
+  </si>
+  <si>
+    <t>muhamad359@gmail.com</t>
+  </si>
+  <si>
+    <t>muhamad176@gmail.com</t>
+  </si>
+  <si>
+    <t>muhammad464@gmail.com</t>
+  </si>
+  <si>
+    <t>muhammad152@gmail.com</t>
+  </si>
+  <si>
+    <t>neneng993@gmail.com</t>
+  </si>
+  <si>
+    <t>rayhan261@gmail.com</t>
+  </si>
+  <si>
+    <t>reno708@gmail.com</t>
+  </si>
+  <si>
+    <t>ridho626@gmail.com</t>
+  </si>
+  <si>
+    <t>rido251@gmail.com</t>
+  </si>
+  <si>
+    <t>rizal507@gmail.com</t>
+  </si>
+  <si>
+    <t>shofiyana666@gmail.com</t>
+  </si>
+  <si>
+    <t>valencia389@gmail.com</t>
+  </si>
+  <si>
+    <t>verry914@gmail.com</t>
+  </si>
+  <si>
+    <t>vina833@gmail.com</t>
+  </si>
+  <si>
+    <t>zairani840@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,12 +752,24 @@
       <family val="1"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color theme="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -114,7 +780,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -122,26 +788,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{1D5FC62F-7208-4405-997F-7DFA4E9B605A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -453,10 +1141,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFAD8768-4066-4A27-B449-170C24190DD5}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.90625" customWidth="1"/>
+    <col min="1" max="1" width="27.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.08984375" customWidth="1"/>
     <col min="3" max="3" width="41.54296875" customWidth="1"/>
     <col min="4" max="4" width="20.08984375" customWidth="1"/>
@@ -465,70 +1153,2232 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="4">
+        <v>20240413</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4">
+        <v>3</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="4">
+        <v>20240414</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4">
+        <v>3</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2">
-        <v>1234500</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2">
-        <v>3</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="B4" s="4">
+        <v>20240415</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="4">
+        <v>3</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2">
-        <v>1234400</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2">
-        <v>3</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="B5" s="4">
+        <v>20240416</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="4">
+        <v>3</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="4">
+        <v>20240417</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="4">
+        <v>3</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="4">
+        <v>20240418</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="4">
+        <v>3</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="4">
+        <v>20240419</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="4">
+        <v>3</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="4">
+        <v>20240420</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="4">
+        <v>3</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="4">
+        <v>20240421</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="4">
+        <v>3</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="4">
+        <v>20240422</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="4">
+        <v>3</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="4">
+        <v>20240423</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4">
+        <v>3</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="4">
+        <v>20240424</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="4">
+        <v>3</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="4">
+        <v>20240425</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="4">
+        <v>3</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="4">
+        <v>20240426</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="4">
+        <v>3</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="4">
+        <v>20240427</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="4">
+        <v>20240428</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="4">
+        <v>3</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="4">
+        <v>20240429</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="4">
+        <v>3</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="4">
+        <v>20240430</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="4">
+        <v>3</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="4">
+        <v>20240431</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="4">
+        <v>3</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="4">
+        <v>20240432</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="4">
+        <v>3</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="4">
+        <v>20240433</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="4">
+        <v>3</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="4">
+        <v>20240434</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="4">
+        <v>3</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="4">
+        <v>20240435</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="4">
+        <v>3</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="4">
+        <v>20240436</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="4">
+        <v>3</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="4">
+        <v>20240437</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="4">
+        <v>3</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="4">
+        <v>20240438</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="4">
+        <v>3</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="4">
+        <v>20240439</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="4">
+        <v>3</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="4">
+        <v>20240440</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="4">
+        <v>3</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="4">
+        <v>20240441</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="4">
+        <v>3</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="4">
+        <v>20240442</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="4">
+        <v>3</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="4">
+        <v>20240443</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="4">
+        <v>3</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="4">
+        <v>20240444</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="4">
+        <v>3</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="4">
+        <v>20240445</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="4">
+        <v>3</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="4">
+        <v>20240446</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="4">
+        <v>3</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="4">
+        <v>20240447</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="4">
+        <v>3</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="4">
+        <v>20240448</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" s="4">
+        <v>3</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="4">
+        <v>20240449</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="4">
+        <v>3</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="4">
+        <v>20240450</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="4">
+        <v>3</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="4">
+        <v>20240451</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="4">
+        <v>3</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="4">
+        <v>20240452</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E41" s="4">
+        <v>3</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="4">
+        <v>20240453</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" s="4">
+        <v>3</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="4">
+        <v>20240454</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E43" s="4">
+        <v>3</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="4">
+        <v>20240455</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E44" s="4">
+        <v>3</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="4">
+        <v>20240456</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E45" s="4">
+        <v>3</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="4">
+        <v>20240457</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E46" s="4">
+        <v>3</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="4">
+        <v>20240458</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E47" s="4">
+        <v>3</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="4">
+        <v>20240459</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E48" s="4">
+        <v>3</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="4">
+        <v>20240460</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E49" s="4">
+        <v>3</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="4">
+        <v>20240461</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E50" s="4">
+        <v>3</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="4">
+        <v>20240462</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" s="4">
+        <v>3</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="4">
+        <v>20240463</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E52" s="4">
+        <v>3</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="4">
+        <v>20240464</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E53" s="4">
+        <v>3</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="4">
+        <v>20240465</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E54" s="4">
+        <v>3</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="4">
+        <v>20240466</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E55" s="4">
+        <v>3</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="4">
+        <v>20240467</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E56" s="4">
+        <v>3</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="4">
+        <v>20240468</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E57" s="4">
+        <v>3</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="4">
+        <v>20240469</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E58" s="4">
+        <v>3</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="4">
+        <v>20240470</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E59" s="4">
+        <v>3</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="4">
+        <v>20240471</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E60" s="4">
+        <v>3</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="4">
+        <v>20240472</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E61" s="4">
+        <v>3</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="4">
+        <v>20240473</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E62" s="4">
+        <v>3</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="4">
+        <v>20240474</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E63" s="4">
+        <v>3</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="4">
+        <v>20240475</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E64" s="4">
+        <v>3</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="4">
+        <v>20240476</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E65" s="4">
+        <v>3</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="4">
+        <v>20240477</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E66" s="4">
+        <v>3</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="4">
+        <v>20240478</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E67" s="4">
+        <v>3</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="4">
+        <v>20240479</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E68" s="4">
+        <v>3</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="4">
+        <v>20240480</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E69" s="4">
+        <v>3</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="4">
+        <v>20240481</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E70" s="4">
+        <v>3</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="4">
+        <v>20240482</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E71" s="4">
+        <v>3</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="4">
+        <v>20240483</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E72" s="4">
+        <v>3</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="4">
+        <v>20240484</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E73" s="4">
+        <v>3</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="4">
+        <v>20240485</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E74" s="4">
+        <v>3</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="4">
+        <v>20240486</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E75" s="4">
+        <v>3</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="4">
+        <v>20240487</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E76" s="4">
+        <v>3</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A77" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="4">
+        <v>20240488</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E77" s="4">
+        <v>3</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A78" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="4">
+        <v>20240489</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E78" s="4">
+        <v>3</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="4">
+        <v>20240490</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E79" s="4">
+        <v>3</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A80" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="4">
+        <v>20240491</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E80" s="4">
+        <v>3</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A81" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="4">
+        <v>20240492</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E81" s="4">
+        <v>3</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A82" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="4">
+        <v>20240493</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E82" s="4">
+        <v>3</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A83" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" s="4">
+        <v>20240494</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E83" s="4">
+        <v>3</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A84" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="4">
+        <v>20240495</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E84" s="4">
+        <v>3</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A85" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="4">
+        <v>20240496</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E85" s="4">
+        <v>3</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A86" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" s="4">
+        <v>20240497</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E86" s="4">
+        <v>3</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A87" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" s="4">
+        <v>20240498</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E87" s="4">
+        <v>3</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A88" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="4">
+        <v>20240499</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E88" s="4">
+        <v>3</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A89" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" s="4">
+        <v>20240500</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E89" s="4">
+        <v>3</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A90" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" s="4">
+        <v>20240501</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E90" s="4">
+        <v>3</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A91" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" s="4">
+        <v>20240502</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E91" s="4">
+        <v>3</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A92" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" s="4">
+        <v>20240503</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E92" s="4">
+        <v>3</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A93" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B93" s="4">
+        <v>20240504</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E93" s="4">
+        <v>3</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A94" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" s="4">
+        <v>20240505</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E94" s="4">
+        <v>3</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A95" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" s="4">
+        <v>20240506</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E95" s="4">
+        <v>3</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A96" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" s="4">
+        <v>20240507</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E96" s="4">
+        <v>3</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A97" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" s="4">
+        <v>20240508</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E97" s="4">
+        <v>3</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A98" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" s="4">
+        <v>20240509</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E98" s="4">
+        <v>3</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A99" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" s="4">
+        <v>20240510</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E99" s="4">
+        <v>3</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A100" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" s="4">
+        <v>20240511</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E100" s="4">
+        <v>3</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A101" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" s="4">
+        <v>20240512</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E101" s="4">
+        <v>3</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A102" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" s="4">
+        <v>20240513</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E102" s="4">
+        <v>3</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A103" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" s="4">
+        <v>20240514</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E103" s="4">
+        <v>3</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A104" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" s="4">
+        <v>20240515</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E104" s="4">
+        <v>3</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A105" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" s="4">
+        <v>20240516</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E105" s="4">
+        <v>3</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A106" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" s="4">
+        <v>20240517</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E106" s="4">
+        <v>3</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A107" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" s="4">
+        <v>20240518</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E107" s="4">
+        <v>3</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A108" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" s="4">
+        <v>20240519</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E108" s="4">
+        <v>3</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A109" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" s="4">
+        <v>20240520</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E109" s="4">
+        <v>3</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A110" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" s="4">
+        <v>20240521</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E110" s="4">
+        <v>3</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A111" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" s="4">
+        <v>20240522</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E111" s="4">
+        <v>3</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C112" s="1"/>
+      <c r="E112" s="1"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{594EAB9A-5281-4D21-A913-7E1655627A94}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{BA4AA428-6DA2-4CE5-94E1-3900680C9464}"/>
-  </hyperlinks>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>